--- a/reference/ref_satker.xlsx
+++ b/reference/ref_satker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/djpb/Downloads/screenshots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5422C3-2FDF-0747-9524-646DB2FD201E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF33BF22-8316-6941-8E86-274E583FB9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15100" yWindow="680" windowWidth="15140" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1757,19 +1757,19 @@
     <t>615081</t>
   </si>
   <si>
-    <t>KOMITE STANDAR AKUNTASI PEMERINTAH (KSAP)</t>
-  </si>
-  <si>
-    <t>BADAN PENGELOLA DANA PERKEBUNAN</t>
-  </si>
-  <si>
     <t>BADAN PENGELOLA DANA LINGKUNGAN HIDUP (BPDLH)</t>
   </si>
   <si>
-    <t>PUSAT INVESTASI PEMERINTAH</t>
-  </si>
-  <si>
-    <t>KOMITE INVESTASI PEMERINTAH</t>
+    <t>KOMITE STANDAR AKUNTANSI PEMERINTAH (KSAP)</t>
+  </si>
+  <si>
+    <t>BADAN PENGELOLA DANA PERKEBUNAN (BPDP)</t>
+  </si>
+  <si>
+    <t>PUSAT INVESTASI PEMERINTAH (PIP)</t>
+  </si>
+  <si>
+    <t>KOMITE INVESTASI PEMERINTAH (KIP)</t>
   </si>
 </sst>
 </file>
@@ -1952,7 +1952,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2014,30 +2014,17 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -14314,152 +14301,157 @@
       <c r="R218" s="21"/>
     </row>
     <row r="219" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A219" s="25" t="s">
+      <c r="A219" s="17" t="s">
         <v>568</v>
       </c>
-      <c r="B219" s="27"/>
-      <c r="C219" s="27"/>
-      <c r="D219" s="29" t="s">
+      <c r="B219" s="7"/>
+      <c r="C219" s="7"/>
+      <c r="D219" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="E219" s="8"/>
+      <c r="F219" s="8"/>
+      <c r="G219" s="8"/>
+      <c r="H219" s="7"/>
+      <c r="I219" s="7"/>
+      <c r="J219" s="7"/>
+      <c r="K219" s="7"/>
+      <c r="L219" s="7"/>
+      <c r="M219" s="7"/>
+      <c r="N219" s="7"/>
+      <c r="O219" s="7"/>
+      <c r="P219" s="9"/>
+      <c r="Q219" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="R219" s="20"/>
+    </row>
+    <row r="220" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A220" s="25" t="s">
+        <v>569</v>
+      </c>
+      <c r="B220" s="26"/>
+      <c r="C220" s="26"/>
+      <c r="D220" s="27" t="s">
+        <v>575</v>
+      </c>
+      <c r="E220" s="27"/>
+      <c r="F220" s="27"/>
+      <c r="G220" s="27"/>
+      <c r="H220" s="26"/>
+      <c r="I220" s="26"/>
+      <c r="J220" s="26"/>
+      <c r="K220" s="26"/>
+      <c r="L220" s="26"/>
+      <c r="M220" s="26"/>
+      <c r="N220" s="26"/>
+      <c r="O220" s="26"/>
+      <c r="P220" s="28"/>
+      <c r="Q220" s="28" t="s">
+        <v>489</v>
+      </c>
+      <c r="R220" s="29"/>
+    </row>
+    <row r="221" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A221" s="25" t="s">
+        <v>570</v>
+      </c>
+      <c r="B221" s="26"/>
+      <c r="C221" s="26"/>
+      <c r="D221" s="27" t="s">
         <v>573</v>
       </c>
-      <c r="E219" s="29"/>
-      <c r="F219" s="29"/>
-      <c r="G219" s="29"/>
-      <c r="H219" s="27"/>
-      <c r="I219" s="27"/>
-      <c r="J219" s="27"/>
-      <c r="K219" s="27"/>
-      <c r="L219" s="27"/>
-      <c r="M219" s="27"/>
-      <c r="N219" s="27"/>
-      <c r="O219" s="27"/>
-      <c r="P219" s="31"/>
-      <c r="Q219" s="31" t="s">
-        <v>500</v>
-      </c>
-      <c r="R219" s="33"/>
-    </row>
-    <row r="220" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A220" s="26" t="s">
-        <v>569</v>
-      </c>
-      <c r="B220" s="28"/>
-      <c r="C220" s="28"/>
-      <c r="D220" s="30" t="s">
-        <v>574</v>
-      </c>
-      <c r="E220" s="30"/>
-      <c r="F220" s="30"/>
-      <c r="G220" s="30"/>
-      <c r="H220" s="28"/>
-      <c r="I220" s="28"/>
-      <c r="J220" s="28"/>
-      <c r="K220" s="28"/>
-      <c r="L220" s="28"/>
-      <c r="M220" s="28"/>
-      <c r="N220" s="28"/>
-      <c r="O220" s="28"/>
-      <c r="P220" s="32"/>
-      <c r="Q220" s="32" t="s">
-        <v>489</v>
-      </c>
-      <c r="R220" s="34"/>
-    </row>
-    <row r="221" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A221" s="26" t="s">
-        <v>570</v>
-      </c>
-      <c r="B221" s="28"/>
-      <c r="C221" s="28"/>
-      <c r="D221" s="30" t="s">
-        <v>575</v>
-      </c>
-      <c r="E221" s="30"/>
-      <c r="F221" s="30"/>
-      <c r="G221" s="30"/>
-      <c r="H221" s="28"/>
-      <c r="I221" s="28"/>
-      <c r="J221" s="28"/>
-      <c r="K221" s="28"/>
-      <c r="L221" s="28"/>
-      <c r="M221" s="28"/>
-      <c r="N221" s="28"/>
-      <c r="O221" s="28"/>
-      <c r="P221" s="32"/>
-      <c r="Q221" s="32" t="s">
+      <c r="E221" s="27"/>
+      <c r="F221" s="27"/>
+      <c r="G221" s="27"/>
+      <c r="H221" s="26"/>
+      <c r="I221" s="26"/>
+      <c r="J221" s="26"/>
+      <c r="K221" s="26"/>
+      <c r="L221" s="26"/>
+      <c r="M221" s="26"/>
+      <c r="N221" s="26"/>
+      <c r="O221" s="26"/>
+      <c r="P221" s="28"/>
+      <c r="Q221" s="28" t="s">
         <v>463</v>
       </c>
-      <c r="R221" s="34"/>
+      <c r="R221" s="29"/>
     </row>
     <row r="222" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A222" s="25" t="s">
+      <c r="A222" s="17" t="s">
         <v>571</v>
       </c>
-      <c r="B222" s="27"/>
-      <c r="C222" s="27"/>
-      <c r="D222" s="29" t="s">
+      <c r="B222" s="7"/>
+      <c r="C222" s="7"/>
+      <c r="D222" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="E222" s="29"/>
-      <c r="F222" s="29"/>
-      <c r="G222" s="29"/>
-      <c r="H222" s="27"/>
-      <c r="I222" s="27"/>
-      <c r="J222" s="27"/>
-      <c r="K222" s="27"/>
-      <c r="L222" s="27"/>
-      <c r="M222" s="27"/>
-      <c r="N222" s="27"/>
-      <c r="O222" s="27"/>
-      <c r="P222" s="31"/>
-      <c r="Q222" s="31" t="s">
+      <c r="E222" s="8"/>
+      <c r="F222" s="8"/>
+      <c r="G222" s="8"/>
+      <c r="H222" s="7"/>
+      <c r="I222" s="7"/>
+      <c r="J222" s="7"/>
+      <c r="K222" s="7"/>
+      <c r="L222" s="7"/>
+      <c r="M222" s="7"/>
+      <c r="N222" s="7"/>
+      <c r="O222" s="7"/>
+      <c r="P222" s="9"/>
+      <c r="Q222" s="9" t="s">
         <v>457</v>
       </c>
-      <c r="R222" s="33"/>
+      <c r="R222" s="20"/>
     </row>
     <row r="223" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A223" s="25" t="s">
+      <c r="A223" s="17" t="s">
         <v>572</v>
       </c>
-      <c r="B223" s="27"/>
-      <c r="C223" s="27"/>
-      <c r="D223" s="35" t="s">
+      <c r="B223" s="7"/>
+      <c r="C223" s="7"/>
+      <c r="D223" s="30" t="s">
         <v>577</v>
       </c>
-      <c r="E223" s="29"/>
-      <c r="F223" s="29"/>
-      <c r="G223" s="29"/>
-      <c r="H223" s="27"/>
-      <c r="I223" s="27"/>
-      <c r="J223" s="27"/>
-      <c r="K223" s="27"/>
-      <c r="L223" s="27"/>
-      <c r="M223" s="27"/>
-      <c r="N223" s="27"/>
-      <c r="O223" s="27"/>
-      <c r="P223" s="31"/>
-      <c r="Q223" s="31" t="s">
+      <c r="E223" s="8"/>
+      <c r="F223" s="8"/>
+      <c r="G223" s="8"/>
+      <c r="H223" s="7"/>
+      <c r="I223" s="7"/>
+      <c r="J223" s="7"/>
+      <c r="K223" s="7"/>
+      <c r="L223" s="7"/>
+      <c r="M223" s="7"/>
+      <c r="N223" s="7"/>
+      <c r="O223" s="7"/>
+      <c r="P223" s="9"/>
+      <c r="Q223" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="R223" s="33"/>
+      <c r="R223" s="20"/>
     </row>
     <row r="224" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E226" s="1" t="b">
+        <f>D226=D219</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
